--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122075745</v>
+        <v>122074987</v>
       </c>
       <c r="B2" t="n">
-        <v>77566</v>
+        <v>78631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441353</v>
+        <v>441407</v>
       </c>
       <c r="R2" t="n">
-        <v>7023876</v>
+        <v>7023986</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122075003</v>
+        <v>122075357</v>
       </c>
       <c r="B3" t="n">
-        <v>77566</v>
+        <v>78631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441407</v>
+        <v>441330</v>
       </c>
       <c r="R3" t="n">
-        <v>7023986</v>
+        <v>7023918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,17 +902,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075551</v>
+        <v>122075205</v>
       </c>
       <c r="B4" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,29 +942,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441362</v>
+        <v>441369</v>
       </c>
       <c r="R4" t="n">
-        <v>7023906</v>
+        <v>7023947</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122074987</v>
+        <v>122075745</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
+        <v>77568</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441407</v>
+        <v>441353</v>
       </c>
       <c r="R5" t="n">
-        <v>7023986</v>
+        <v>7023876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075357</v>
+        <v>122075448</v>
       </c>
       <c r="B6" t="n">
-        <v>78629</v>
+        <v>77568</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441330</v>
+        <v>441345</v>
       </c>
       <c r="R6" t="n">
-        <v>7023918</v>
+        <v>7023899</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122075448</v>
+        <v>122075628</v>
       </c>
       <c r="B7" t="n">
-        <v>77566</v>
+        <v>90709</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,25 +1272,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,13 +1300,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441345</v>
+        <v>441350</v>
       </c>
       <c r="R7" t="n">
-        <v>7023899</v>
+        <v>7023868</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,22 +1365,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075205</v>
+        <v>122075551</v>
       </c>
       <c r="B8" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,20 +1410,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441369</v>
+        <v>441362</v>
       </c>
       <c r="R8" t="n">
-        <v>7023947</v>
+        <v>7023906</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1486,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075628</v>
+        <v>122075003</v>
       </c>
       <c r="B9" t="n">
-        <v>90707</v>
+        <v>77568</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,25 +1510,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441350</v>
+        <v>441407</v>
       </c>
       <c r="R9" t="n">
-        <v>7023868</v>
+        <v>7023986</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122074987</v>
+        <v>122075551</v>
       </c>
       <c r="B2" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,20 +708,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441407</v>
+        <v>441362</v>
       </c>
       <c r="R2" t="n">
-        <v>7023986</v>
+        <v>7023906</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122075357</v>
+        <v>122075628</v>
       </c>
       <c r="B3" t="n">
-        <v>78631</v>
+        <v>90710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441330</v>
+        <v>441350</v>
       </c>
       <c r="R3" t="n">
-        <v>7023918</v>
+        <v>7023868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,17 +906,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075205</v>
+        <v>122075448</v>
       </c>
       <c r="B4" t="n">
-        <v>78631</v>
+        <v>77569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441369</v>
+        <v>441345</v>
       </c>
       <c r="R4" t="n">
-        <v>7023947</v>
+        <v>7023899</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122075745</v>
+        <v>122075357</v>
       </c>
       <c r="B5" t="n">
-        <v>77568</v>
+        <v>78632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441353</v>
+        <v>441330</v>
       </c>
       <c r="R5" t="n">
-        <v>7023876</v>
+        <v>7023918</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,17 +1140,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075448</v>
+        <v>122075745</v>
       </c>
       <c r="B6" t="n">
-        <v>77568</v>
+        <v>77569</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441345</v>
+        <v>441353</v>
       </c>
       <c r="R6" t="n">
-        <v>7023899</v>
+        <v>7023876</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1252,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122075628</v>
+        <v>122075205</v>
       </c>
       <c r="B7" t="n">
-        <v>90709</v>
+        <v>78632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,25 +1276,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441350</v>
+        <v>441369</v>
       </c>
       <c r="R7" t="n">
-        <v>7023868</v>
+        <v>7023947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075551</v>
+        <v>122075003</v>
       </c>
       <c r="B8" t="n">
-        <v>78631</v>
+        <v>77569</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,46 +1397,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441362</v>
+        <v>441407</v>
       </c>
       <c r="R8" t="n">
-        <v>7023906</v>
+        <v>7023986</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1486,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075003</v>
+        <v>122074987</v>
       </c>
       <c r="B9" t="n">
-        <v>77568</v>
+        <v>78632</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,21 +1514,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122075551</v>
+        <v>122075745</v>
       </c>
       <c r="B2" t="n">
-        <v>78632</v>
+        <v>77576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441362</v>
+        <v>441353</v>
       </c>
       <c r="R2" t="n">
-        <v>7023906</v>
+        <v>7023876</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122075628</v>
+        <v>122075357</v>
       </c>
       <c r="B3" t="n">
-        <v>90710</v>
+        <v>78639</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441350</v>
+        <v>441330</v>
       </c>
       <c r="R3" t="n">
-        <v>7023868</v>
+        <v>7023918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,17 +902,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075448</v>
+        <v>122075551</v>
       </c>
       <c r="B4" t="n">
-        <v>77569</v>
+        <v>78639</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,37 +925,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441345</v>
+        <v>441362</v>
       </c>
       <c r="R4" t="n">
-        <v>7023899</v>
+        <v>7023906</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,17 +1023,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122075357</v>
+        <v>122075003</v>
       </c>
       <c r="B5" t="n">
-        <v>78632</v>
+        <v>77576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441330</v>
+        <v>441407</v>
       </c>
       <c r="R5" t="n">
-        <v>7023918</v>
+        <v>7023986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,17 +1140,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075745</v>
+        <v>122075205</v>
       </c>
       <c r="B6" t="n">
-        <v>77569</v>
+        <v>78639</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,21 +1163,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441353</v>
+        <v>441369</v>
       </c>
       <c r="R6" t="n">
-        <v>7023876</v>
+        <v>7023947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122075205</v>
+        <v>122074987</v>
       </c>
       <c r="B7" t="n">
-        <v>78632</v>
+        <v>78639</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441369</v>
+        <v>441407</v>
       </c>
       <c r="R7" t="n">
-        <v>7023947</v>
+        <v>7023986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075003</v>
+        <v>122075448</v>
       </c>
       <c r="B8" t="n">
-        <v>77569</v>
+        <v>77576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441407</v>
+        <v>441345</v>
       </c>
       <c r="R8" t="n">
-        <v>7023986</v>
+        <v>7023899</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1486,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122074987</v>
+        <v>122075628</v>
       </c>
       <c r="B9" t="n">
-        <v>78632</v>
+        <v>90719</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,25 +1510,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441407</v>
+        <v>441350</v>
       </c>
       <c r="R9" t="n">
-        <v>7023986</v>
+        <v>7023868</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122075745</v>
+        <v>122074987</v>
       </c>
       <c r="B2" t="n">
-        <v>77576</v>
+        <v>78643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441353</v>
+        <v>441407</v>
       </c>
       <c r="R2" t="n">
-        <v>7023876</v>
+        <v>7023986</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>122075357</v>
       </c>
       <c r="B3" t="n">
-        <v>78639</v>
+        <v>78643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075551</v>
+        <v>122075448</v>
       </c>
       <c r="B4" t="n">
-        <v>78639</v>
+        <v>77580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,46 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441362</v>
+        <v>441345</v>
       </c>
       <c r="R4" t="n">
-        <v>7023906</v>
+        <v>7023899</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,17 +1019,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122075003</v>
+        <v>122075628</v>
       </c>
       <c r="B5" t="n">
-        <v>77576</v>
+        <v>90726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441407</v>
+        <v>441350</v>
       </c>
       <c r="R5" t="n">
-        <v>7023986</v>
+        <v>7023868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075205</v>
+        <v>122075745</v>
       </c>
       <c r="B6" t="n">
-        <v>78639</v>
+        <v>77580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441369</v>
+        <v>441353</v>
       </c>
       <c r="R6" t="n">
-        <v>7023947</v>
+        <v>7023876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122074987</v>
+        <v>122075003</v>
       </c>
       <c r="B7" t="n">
-        <v>78639</v>
+        <v>77580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1354,7 +1350,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075448</v>
+        <v>122075551</v>
       </c>
       <c r="B8" t="n">
-        <v>77576</v>
+        <v>78643</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,37 +1393,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441345</v>
+        <v>441362</v>
       </c>
       <c r="R8" t="n">
-        <v>7023899</v>
+        <v>7023906</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075628</v>
+        <v>122075205</v>
       </c>
       <c r="B9" t="n">
-        <v>90719</v>
+        <v>78643</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,25 +1510,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441350</v>
+        <v>441369</v>
       </c>
       <c r="R9" t="n">
-        <v>7023868</v>
+        <v>7023947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122074987</v>
+        <v>122075205</v>
       </c>
       <c r="B2" t="n">
-        <v>78643</v>
+        <v>78645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441407</v>
+        <v>441369</v>
       </c>
       <c r="R2" t="n">
-        <v>7023986</v>
+        <v>7023947</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122075357</v>
+        <v>122075003</v>
       </c>
       <c r="B3" t="n">
-        <v>78643</v>
+        <v>77582</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441330</v>
+        <v>441407</v>
       </c>
       <c r="R3" t="n">
-        <v>7023918</v>
+        <v>7023986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -912,7 +912,7 @@
         <v>122075448</v>
       </c>
       <c r="B4" t="n">
-        <v>77580</v>
+        <v>77582</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122075628</v>
+        <v>122074987</v>
       </c>
       <c r="B5" t="n">
-        <v>90726</v>
+        <v>78645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441350</v>
+        <v>441407</v>
       </c>
       <c r="R5" t="n">
-        <v>7023868</v>
+        <v>7023986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075745</v>
+        <v>122075551</v>
       </c>
       <c r="B6" t="n">
-        <v>77580</v>
+        <v>78645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,37 +1159,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441353</v>
+        <v>441362</v>
       </c>
       <c r="R6" t="n">
-        <v>7023876</v>
+        <v>7023906</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1252,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122075003</v>
+        <v>122075745</v>
       </c>
       <c r="B7" t="n">
-        <v>77580</v>
+        <v>77582</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441407</v>
+        <v>441353</v>
       </c>
       <c r="R7" t="n">
-        <v>7023986</v>
+        <v>7023876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,17 +1374,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075551</v>
+        <v>122075628</v>
       </c>
       <c r="B8" t="n">
-        <v>78643</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,50 +1393,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441362</v>
+        <v>441350</v>
       </c>
       <c r="R8" t="n">
-        <v>7023906</v>
+        <v>7023868</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1486,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075205</v>
+        <v>122075357</v>
       </c>
       <c r="B9" t="n">
-        <v>78643</v>
+        <v>78645</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441369</v>
+        <v>441330</v>
       </c>
       <c r="R9" t="n">
-        <v>7023947</v>
+        <v>7023918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122075205</v>
+        <v>122075357</v>
       </c>
       <c r="B2" t="n">
         <v>78645</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441369</v>
+        <v>441330</v>
       </c>
       <c r="R2" t="n">
-        <v>7023947</v>
+        <v>7023918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,14 +785,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122075003</v>
+        <v>122075448</v>
       </c>
       <c r="B3" t="n">
         <v>77582</v>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441407</v>
+        <v>441345</v>
       </c>
       <c r="R3" t="n">
-        <v>7023986</v>
+        <v>7023899</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075448</v>
+        <v>122075003</v>
       </c>
       <c r="B4" t="n">
         <v>77582</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441345</v>
+        <v>441407</v>
       </c>
       <c r="R4" t="n">
-        <v>7023899</v>
+        <v>7023986</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122074987</v>
+        <v>122075628</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441407</v>
+        <v>441350</v>
       </c>
       <c r="R5" t="n">
-        <v>7023986</v>
+        <v>7023868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075551</v>
+        <v>122075745</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>77582</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,46 +1159,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441362</v>
+        <v>441353</v>
       </c>
       <c r="R6" t="n">
-        <v>7023906</v>
+        <v>7023876</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122075745</v>
+        <v>122075205</v>
       </c>
       <c r="B7" t="n">
-        <v>77582</v>
+        <v>78645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441353</v>
+        <v>441369</v>
       </c>
       <c r="R7" t="n">
-        <v>7023876</v>
+        <v>7023947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,17 +1370,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075628</v>
+        <v>122074987</v>
       </c>
       <c r="B8" t="n">
-        <v>90728</v>
+        <v>78645</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,25 +1389,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441350</v>
+        <v>441407</v>
       </c>
       <c r="R8" t="n">
-        <v>7023868</v>
+        <v>7023986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075357</v>
+        <v>122075551</v>
       </c>
       <c r="B9" t="n">
         <v>78645</v>
@@ -1531,20 +1527,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441330</v>
+        <v>441362</v>
       </c>
       <c r="R9" t="n">
-        <v>7023918</v>
+        <v>7023906</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1603,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122075745</v>
+        <v>122074987</v>
       </c>
       <c r="B3" t="n">
-        <v>77582</v>
+        <v>78645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441353</v>
+        <v>441407</v>
       </c>
       <c r="R3" t="n">
-        <v>7023876</v>
+        <v>7023986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075205</v>
+        <v>122075745</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>77582</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441369</v>
+        <v>441353</v>
       </c>
       <c r="R4" t="n">
-        <v>7023947</v>
+        <v>7023876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122075448</v>
+        <v>122075551</v>
       </c>
       <c r="B5" t="n">
-        <v>77582</v>
+        <v>78645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,37 +1042,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441345</v>
+        <v>441362</v>
       </c>
       <c r="R5" t="n">
-        <v>7023899</v>
+        <v>7023906</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,17 +1140,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075551</v>
+        <v>122075628</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>90744</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,50 +1159,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441362</v>
+        <v>441350</v>
       </c>
       <c r="R6" t="n">
-        <v>7023906</v>
+        <v>7023868</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,22 +1252,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122075003</v>
+        <v>122075205</v>
       </c>
       <c r="B7" t="n">
-        <v>77582</v>
+        <v>78645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1280,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441407</v>
+        <v>441369</v>
       </c>
       <c r="R7" t="n">
-        <v>7023986</v>
+        <v>7023947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122074987</v>
+        <v>122075448</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>77582</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,21 +1397,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441407</v>
+        <v>441345</v>
       </c>
       <c r="R8" t="n">
-        <v>7023986</v>
+        <v>7023899</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1486,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075628</v>
+        <v>122075003</v>
       </c>
       <c r="B9" t="n">
-        <v>90744</v>
+        <v>77582</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,25 +1510,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441350</v>
+        <v>441407</v>
       </c>
       <c r="R9" t="n">
-        <v>7023868</v>
+        <v>7023986</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122075357</v>
+        <v>122075205</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441330</v>
+        <v>441369</v>
       </c>
       <c r="R2" t="n">
-        <v>7023918</v>
+        <v>7023947</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>122074987</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075745</v>
+        <v>122075003</v>
       </c>
       <c r="B4" t="n">
-        <v>77582</v>
+        <v>77583</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441353</v>
+        <v>441407</v>
       </c>
       <c r="R4" t="n">
-        <v>7023876</v>
+        <v>7023986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122075551</v>
+        <v>122075628</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>90754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,50 +1038,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441362</v>
+        <v>441350</v>
       </c>
       <c r="R5" t="n">
-        <v>7023906</v>
+        <v>7023868</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075628</v>
+        <v>122075357</v>
       </c>
       <c r="B6" t="n">
-        <v>90744</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,25 +1155,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441350</v>
+        <v>441330</v>
       </c>
       <c r="R6" t="n">
-        <v>7023868</v>
+        <v>7023918</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,17 +1253,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122075205</v>
+        <v>122075745</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>77583</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441369</v>
+        <v>441353</v>
       </c>
       <c r="R7" t="n">
-        <v>7023947</v>
+        <v>7023876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075448</v>
+        <v>122075551</v>
       </c>
       <c r="B8" t="n">
-        <v>77582</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,37 +1393,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441345</v>
+        <v>441362</v>
       </c>
       <c r="R8" t="n">
-        <v>7023899</v>
+        <v>7023906</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075003</v>
+        <v>122075448</v>
       </c>
       <c r="B9" t="n">
-        <v>77582</v>
+        <v>77583</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441407</v>
+        <v>441345</v>
       </c>
       <c r="R9" t="n">
-        <v>7023986</v>
+        <v>7023899</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1603,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122075205</v>
+        <v>122075448</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>77583</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441369</v>
+        <v>441345</v>
       </c>
       <c r="R2" t="n">
-        <v>7023947</v>
+        <v>7023899</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122074987</v>
+        <v>122075628</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>90754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441407</v>
+        <v>441350</v>
       </c>
       <c r="R3" t="n">
-        <v>7023986</v>
+        <v>7023868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075003</v>
+        <v>122075357</v>
       </c>
       <c r="B4" t="n">
-        <v>77583</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441407</v>
+        <v>441330</v>
       </c>
       <c r="R4" t="n">
-        <v>7023986</v>
+        <v>7023918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122075628</v>
+        <v>122074987</v>
       </c>
       <c r="B5" t="n">
-        <v>90754</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441350</v>
+        <v>441407</v>
       </c>
       <c r="R5" t="n">
-        <v>7023868</v>
+        <v>7023986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075357</v>
+        <v>122075551</v>
       </c>
       <c r="B6" t="n">
         <v>78646</v>
@@ -1176,20 +1176,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441330</v>
+        <v>441362</v>
       </c>
       <c r="R6" t="n">
-        <v>7023918</v>
+        <v>7023906</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1252,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122075745</v>
+        <v>122075205</v>
       </c>
       <c r="B7" t="n">
-        <v>77583</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1280,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441353</v>
+        <v>441369</v>
       </c>
       <c r="R7" t="n">
-        <v>7023876</v>
+        <v>7023947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075551</v>
+        <v>122075745</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>77583</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,46 +1397,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441362</v>
+        <v>441353</v>
       </c>
       <c r="R8" t="n">
-        <v>7023906</v>
+        <v>7023876</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,19 +1486,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075448</v>
+        <v>122075003</v>
       </c>
       <c r="B9" t="n">
         <v>77583</v>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441345</v>
+        <v>441407</v>
       </c>
       <c r="R9" t="n">
-        <v>7023899</v>
+        <v>7023986</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1603,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122075628</v>
+        <v>122075357</v>
       </c>
       <c r="B3" t="n">
-        <v>90754</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441350</v>
+        <v>441330</v>
       </c>
       <c r="R3" t="n">
-        <v>7023868</v>
+        <v>7023918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,17 +902,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075357</v>
+        <v>122075628</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>90754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441330</v>
+        <v>441350</v>
       </c>
       <c r="R4" t="n">
-        <v>7023918</v>
+        <v>7023868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122075448</v>
+        <v>122075003</v>
       </c>
       <c r="B2" t="n">
-        <v>77583</v>
+        <v>77588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441345</v>
+        <v>441407</v>
       </c>
       <c r="R2" t="n">
-        <v>7023899</v>
+        <v>7023986</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122075357</v>
+        <v>122074987</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441330</v>
+        <v>441407</v>
       </c>
       <c r="R3" t="n">
-        <v>7023918</v>
+        <v>7023986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,17 +902,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075628</v>
+        <v>122075448</v>
       </c>
       <c r="B4" t="n">
-        <v>90754</v>
+        <v>77588</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441350</v>
+        <v>441345</v>
       </c>
       <c r="R4" t="n">
-        <v>7023868</v>
+        <v>7023899</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122074987</v>
+        <v>122075551</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,20 +1059,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441407</v>
+        <v>441362</v>
       </c>
       <c r="R5" t="n">
-        <v>7023986</v>
+        <v>7023906</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1135,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075551</v>
+        <v>122075357</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,29 +1180,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441362</v>
+        <v>441330</v>
       </c>
       <c r="R6" t="n">
-        <v>7023906</v>
+        <v>7023918</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,12 +1252,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1267,7 +1267,7 @@
         <v>122075205</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>122075745</v>
       </c>
       <c r="B8" t="n">
-        <v>77583</v>
+        <v>77588</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075003</v>
+        <v>122075628</v>
       </c>
       <c r="B9" t="n">
-        <v>77583</v>
+        <v>90766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,25 +1510,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441407</v>
+        <v>441350</v>
       </c>
       <c r="R9" t="n">
-        <v>7023986</v>
+        <v>7023868</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122075003</v>
+        <v>122075628</v>
       </c>
       <c r="B2" t="n">
-        <v>77588</v>
+        <v>90773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441407</v>
+        <v>441350</v>
       </c>
       <c r="R2" t="n">
-        <v>7023986</v>
+        <v>7023868</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På död gren på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075448</v>
+        <v>122075205</v>
       </c>
       <c r="B4" t="n">
-        <v>77588</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441345</v>
+        <v>441369</v>
       </c>
       <c r="R4" t="n">
-        <v>7023899</v>
+        <v>7023947</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122075551</v>
+        <v>122075448</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>77588</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,46 +1042,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441362</v>
+        <v>441345</v>
       </c>
       <c r="R5" t="n">
-        <v>7023906</v>
+        <v>7023899</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,17 +1136,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075357</v>
+        <v>122075003</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>77588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441330</v>
+        <v>441407</v>
       </c>
       <c r="R6" t="n">
-        <v>7023918</v>
+        <v>7023986</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,17 +1253,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122075205</v>
+        <v>122075745</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>77588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441369</v>
+        <v>441353</v>
       </c>
       <c r="R7" t="n">
-        <v>7023947</v>
+        <v>7023876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075745</v>
+        <v>122075551</v>
       </c>
       <c r="B8" t="n">
-        <v>77588</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,37 +1393,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441353</v>
+        <v>441362</v>
       </c>
       <c r="R8" t="n">
-        <v>7023876</v>
+        <v>7023906</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1486,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075628</v>
+        <v>122075357</v>
       </c>
       <c r="B9" t="n">
-        <v>90766</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,25 +1510,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441350</v>
+        <v>441330</v>
       </c>
       <c r="R9" t="n">
-        <v>7023868</v>
+        <v>7023918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran i gammal barrblandskog</t>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122075628</v>
       </c>
       <c r="B2" t="n">
-        <v>90773</v>
+        <v>90778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>5447</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122074987</v>
+        <v>122075551</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,11 +805,6 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -825,20 +815,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441407</v>
+        <v>441362</v>
       </c>
       <c r="R3" t="n">
-        <v>7023986</v>
+        <v>7023906</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122075205</v>
+        <v>122074987</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,11 +921,6 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -949,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441369</v>
+        <v>441407</v>
       </c>
       <c r="R4" t="n">
-        <v>7023947</v>
+        <v>7023986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +983,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122075448</v>
+        <v>122075357</v>
       </c>
       <c r="B5" t="n">
-        <v>77588</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441345</v>
+        <v>441330</v>
       </c>
       <c r="R5" t="n">
-        <v>7023899</v>
+        <v>7023918</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075003</v>
+        <v>122075205</v>
       </c>
       <c r="B6" t="n">
-        <v>77588</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1143,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441407</v>
+        <v>441369</v>
       </c>
       <c r="R6" t="n">
-        <v>7023986</v>
+        <v>7023947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,7 +1242,7 @@
         <v>122075745</v>
       </c>
       <c r="B7" t="n">
-        <v>77588</v>
+        <v>77589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,11 +1256,6 @@
       </c>
       <c r="E7" t="n">
         <v>228579</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1377,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075551</v>
+        <v>122075003</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>77589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,46 +1367,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>228579</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441362</v>
+        <v>441407</v>
       </c>
       <c r="R8" t="n">
-        <v>7023906</v>
+        <v>7023986</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1431,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1451,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075357</v>
+        <v>122075448</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>77589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,21 +1479,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>228579</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,13 +1498,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441330</v>
+        <v>441345</v>
       </c>
       <c r="R9" t="n">
-        <v>7023918</v>
+        <v>7023899</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal tall, ca 200 år i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1563,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122075628</v>
       </c>
       <c r="B2" t="n">
-        <v>90778</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -692,6 +687,11 @@
       </c>
       <c r="E2" t="n">
         <v>5447</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -787,24 +787,24 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122075551</v>
+        <v>122074987</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6425</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -815,29 +815,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441362</v>
+        <v>441407</v>
       </c>
       <c r="R3" t="n">
-        <v>7023906</v>
+        <v>7023986</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,36 +887,36 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122074987</v>
+        <v>122075205</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>6425</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -938,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441407</v>
+        <v>441369</v>
       </c>
       <c r="R4" t="n">
-        <v>7023986</v>
+        <v>7023947</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran (22 cm dbh, ca 150 år gammal) i gammal barrblandskog</t>
+          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,20 +1014,20 @@
         <v>122075357</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1127,24 +1123,24 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122075205</v>
+        <v>122075551</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>6425</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1155,20 +1151,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren, Stormyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441369</v>
+        <v>441362</v>
       </c>
       <c r="R6" t="n">
-        <v>7023947</v>
+        <v>7023906</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal gran (18 cm dbh, ca 200 år) i gammal barrblandskog</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,27 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122075745</v>
+        <v>122075003</v>
       </c>
       <c r="B7" t="n">
-        <v>77589</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,6 +1252,11 @@
       <c r="E7" t="n">
         <v>228579</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Chaenothecopsis nana</t>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441353</v>
+        <v>441407</v>
       </c>
       <c r="R7" t="n">
-        <v>7023876</v>
+        <v>7023986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,15 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122075003</v>
+        <v>122075448</v>
       </c>
       <c r="B8" t="n">
-        <v>77589</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,6 +1364,11 @@
       <c r="E8" t="n">
         <v>228579</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Chaenothecopsis nana</t>
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441407</v>
+        <v>441345</v>
       </c>
       <c r="R8" t="n">
-        <v>7023986</v>
+        <v>7023899</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,27 +1451,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122075448</v>
+        <v>122075745</v>
       </c>
       <c r="B9" t="n">
-        <v>77589</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,6 +1476,11 @@
       <c r="E9" t="n">
         <v>228579</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Chaenothecopsis nana</t>
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441345</v>
+        <v>441353</v>
       </c>
       <c r="R9" t="n">
-        <v>7023899</v>
+        <v>7023876</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,12 +1563,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 52588-2024 artfynd.xlsx
+++ b/artfynd/A 52588-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122075628</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122074987</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122075205</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122075357</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122075551</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122075003</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122075448</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1572,8 +1612,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122075745</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>